--- a/docs/db_schema_toolbox45.xlsx
+++ b/docs/db_schema_toolbox45.xlsx
@@ -3521,9 +3521,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002763A2ADDABD8145B918A552381C032F" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="99d566f5e2782b61271cd18c9ade5b6b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f9fdd3d-3b0e-4276-9d83-cb3206a3dfa6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="19bed779e70ad4cea1085d4062770ee0" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002763A2ADDABD8145B918A552381C032F" ma:contentTypeVersion="9" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="49b661aefaee09e00ed6c317186eee31">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f9fdd3d-3b0e-4276-9d83-cb3206a3dfa6" xmlns:ns3="dcd90417-dc21-45e5-beb1-a6d98a49a66b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1c0174c4642ea143b29a45a31cf95964" ns2:_="" ns3:_="">
     <xsd:import namespace="2f9fdd3d-3b0e-4276-9d83-cb3206a3dfa6"/>
+    <xsd:import namespace="dcd90417-dc21-45e5-beb1-a6d98a49a66b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -3533,6 +3534,11 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3557,6 +3563,43 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="26fc1f3d-6bf6-4595-a5e0-549689830168" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dcd90417-dc21-45e5-beb1-a6d98a49a66b" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f7ec1839-bf50-4964-8210-65c1cfc23807}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dcd90417-dc21-45e5-beb1-a6d98a49a66b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -3669,12 +3712,17 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <TaxCatchAll xmlns="dcd90417-dc21-45e5-beb1-a6d98a49a66b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f9fdd3d-3b0e-4276-9d83-cb3206a3dfa6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A65D6FA2-AE96-4E7E-9863-B250FB660AC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{802F390C-6912-4C31-85A4-5289F9D76CA0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
